--- a/Sullivan Dashboard/Raw Data/Ethiopian/Mainline Aviation - ET Invoice NEW revised.xlsx
+++ b/Sullivan Dashboard/Raw Data/Ethiopian/Mainline Aviation - ET Invoice NEW revised.xlsx
@@ -41380,10 +41380,10 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACC1F5A0A416614B82852BE73669C751" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a8ed02de0b03959a2e30e5d42120411a">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="173d4cca-d12e-42be-98eb-9d55375e886e" xmlns:ns3="1b20320e-5bc9-4dea-9abd-7bcacf0c9240" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d5088bc808739f0fc7afffb3b9015931" ns2:_="" ns3:_="">
-    <xsd:import namespace="173d4cca-d12e-42be-98eb-9d55375e886e"/>
-    <xsd:import namespace="1b20320e-5bc9-4dea-9abd-7bcacf0c9240"/>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000560CDE7020FBE4F987D5680CBA97CD3" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4fbed0173a2ebcc74ba7d005722587c6">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="042478ca-ca2d-4d01-83eb-90396d5625e9" xmlns:ns3="70b03f2f-74c7-4926-a36d-d4bdb9e02d45" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1e47617018f8bf8a4d157a39e72236d1" ns2:_="" ns3:_="">
+    <xsd:import namespace="042478ca-ca2d-4d01-83eb-90396d5625e9"/>
+    <xsd:import namespace="70b03f2f-74c7-4926-a36d-d4bdb9e02d45"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
@@ -41392,17 +41392,13 @@
               <xsd:all>
                 <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -41410,7 +41406,7 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="173d4cca-d12e-42be-98eb-9d55375e886e" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="042478ca-ca2d-4d01-83eb-90396d5625e9" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
@@ -41423,81 +41419,45 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="13" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="15" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="c5be1fd7-7535-4a18-99f7-c6c8bb01b25e" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="00000000-0000-0000-0000-000000000000" ma:termSetId="00000000-0000-0000-0000-000000000000" ma:anchorId="00000000-0000-0000-0000-000000000000" ma:open="false" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
         </xsd:sequence>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="18" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+    <xsd:element name="MediaServiceOCR" ma:index="16" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="19" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="20" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="21" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="1b20320e-5bc9-4dea-9abd-7bcacf0c9240" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="70b03f2f-74c7-4926-a36d-d4bdb9e02d45" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="11" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="12" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="16" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{98cece4b-9492-46de-83fe-01450af52f2b}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="1b20320e-5bc9-4dea-9abd-7bcacf0c9240">
+    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{a7cd25fd-8387-47a0-a3a2-f48b21d35c24}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="70b03f2f-74c7-4926-a36d-d4bdb9e02d45">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:MultiChoiceLookup">
@@ -41620,31 +41580,16 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="173d4cca-d12e-42be-98eb-9d55375e886e">
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="042478ca-ca2d-4d01-83eb-90396d5625e9">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="1b20320e-5bc9-4dea-9abd-7bcacf0c9240" xsi:nil="true"/>
+    <TaxCatchAll xmlns="70b03f2f-74c7-4926-a36d-d4bdb9e02d45" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45BDE17A-4D07-4317-9FB8-5BB77D828A14}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="173d4cca-d12e-42be-98eb-9d55375e886e"/>
-    <ds:schemaRef ds:uri="1b20320e-5bc9-4dea-9abd-7bcacf0c9240"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78385CB7-734A-4BCB-85C8-D8D76BCF7C45}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
